--- a/static/excel/PEP_model.xlsx
+++ b/static/excel/PEP_model.xlsx
@@ -7367,11 +7367,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>203469.14716</v>
+        <v>205820.313597</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $148.85</t>
+          <t>FMP marketCap  |  price $150.57</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-20</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.196</v>
+        <v>1.193</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="B20" s="51" t="n">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
@@ -7823,16 +7823,16 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B44" s="55">
-        <f>B8*B28+B9*B37*(1-B41)</f>
+        <f>MAX(0.085, B8*B28+B9*B37*(1-B41))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="B38" s="101" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="C38" s="99" t="n"/>
       <c r="D38" s="99" t="n"/>
@@ -9475,7 +9475,7 @@
       <c r="L38" s="99" t="n"/>
       <c r="M38" s="74" t="inlineStr">
         <is>
-          <t>Growth tier: LOW (2.9% 3yr avg rev growth).  Bear 8x / Base 10x / Bull 12x.  Override manually if needed.</t>
+          <t>Growth tier: LOW (2.9% 3yr avg rev growth).  Bear 11x / Base 14x / Bull 16x.  Override manually if needed.</t>
         </is>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>148.85</v>
+        <v>150.57</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10077,7 +10077,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — PEP  |  Master Prompt v2  |  22 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — PEP  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 23.9x  |  5yr avg 26.2x  |  DCF-implied 19.6x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.32 | no_fwd_data(fallback) | abs=7.0 → blended 40/40/20=8.05]  PEG≈845.75 (trailing_pe=23.9x / rev_cagr=3%, revenue proxy)</t>
+          <t>Current 23.9x  |  5yr avg 26.2x  |  DCF-implied 13.2x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.32 | fwd_pe=17.4x→10.00 | abs=7.0 → blended 40/40/20=8.73]  PEG=39.90 (fwd_pe=17.4x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="135" t="inlineStr">
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>8.050000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 23.9x  |  5yr avg 26.2x  |  DCF-implied 19.6x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.32 | no_fwd_data(fallback) | abs=7.0 → blended 40/40/20=8.05]  PEG≈845.75 (trailing_pe=23.9x / rev_cagr=3%, revenue proxy)</t>
+          <t>Current 23.9x  |  5yr avg 26.2x  |  DCF-implied 13.2x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.32 | fwd_pe=17.4x→10.00 | abs=7.0 → blended 40/40/20=8.73]  PEG=39.90 (fwd_pe=17.4x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 25.6x  |  5yr avg 32.6x  |  DCF-implied 21.0x [ref only — not used as benchmark]  [-21% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=7.5 → blended 40/40/20=9.50]  [fcf_yield=3.9% vs rf=4.6%  spread=-0.7%→modifier=-0.25]</t>
+          <t>Current 25.6x  |  5yr avg 32.6x  |  DCF-implied 14.2x [ref only — not used as benchmark]  [-21% vs benchmark]  [trail=10.00 | fwd_pfcf=25.4x→10.00 | abs=7.5 → blended 40/40/20=9.50]  [fcf_yield=3.9% vs rf=4.6%  spread=-0.7%→modifier=-0.25]</t>
         </is>
       </c>
       <c r="E23" s="131" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 25.6x  |  5yr avg 32.6x  |  DCF-implied 21.0x [ref only — not used as benchmark]  [-21% vs benchmark]  [trail=10.00 | no_fwd_data(fallback) | abs=7.5 → blended 40/40/20=9.50]  [fcf_yield=3.9% vs rf=4.6%  spread=-0.7%→modifier=-0.25]</t>
+          <t>Current 25.6x  |  5yr avg 32.6x  |  DCF-implied 14.2x [ref only — not used as benchmark]  [-21% vs benchmark]  [trail=10.00 | fwd_pfcf=25.4x→10.00 | abs=7.5 → blended 40/40/20=9.50]  [fcf_yield=3.9% vs rf=4.6%  spread=-0.7%→modifier=-0.25]</t>
         </is>
       </c>
     </row>

--- a/static/excel/PEP_model.xlsx
+++ b/static/excel/PEP_model.xlsx
@@ -7453,11 +7453,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7667,25 +7667,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0507</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A3CAEY — A</t>
         </is>
       </c>
     </row>
@@ -7728,11 +7730,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0529</v>
+        <v>0.05279999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.72%</t>
+          <t>Rf 4.56% + spread 0.72%</t>
         </is>
       </c>
     </row>
@@ -7758,11 +7760,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0384</v>
+        <v>0.0425</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10079,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — PEP  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — PEP  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10594,16 +10596,16 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 23.9x  |  5yr avg 26.2x  |  DCF-implied 13.2x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.32 | fwd_pe=17.4x→10.00 | abs=7.0 → blended 40/40/20=8.73]  PEG=39.90 (fwd_pe=17.4x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
-      <c r="E22" s="135" t="inlineStr">
-        <is>
-          <t>MOD-HIGH</t>
+          <t>Fwd P/E 17.4x (scoring basis)  |  5yr avg 25.7x  |  DCF-implied 13.2x [ref only — not used as benchmark]  [-32% vs benchmark]  [trail=10.00 | fwd_pe=17.4x→10.00 | abs=10.0 → blended 40/40/20=10.00]  PEG=39.90 (fwd_pe=17.4x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
+        </is>
+      </c>
+      <c r="E22" s="131" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>9.23</v>
+        <v>10.5</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10611,7 +10613,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 23.9x  |  5yr avg 26.2x  |  DCF-implied 13.2x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.32 | fwd_pe=17.4x→10.00 | abs=7.0 → blended 40/40/20=8.73]  PEG=39.90 (fwd_pe=17.4x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 17.4x (scoring basis)  |  5yr avg 25.7x  |  DCF-implied 13.2x [ref only — not used as benchmark]  [-32% vs benchmark]  [trail=10.00 | fwd_pe=17.4x→10.00 | abs=10.0 → blended 40/40/20=10.00]  PEG=39.90 (fwd_pe=17.4x / eps_growth=44%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10633,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 25.6x  |  5yr avg 32.6x  |  DCF-implied 14.2x [ref only — not used as benchmark]  [-21% vs benchmark]  [trail=10.00 | fwd_pfcf=25.4x→10.00 | abs=7.5 → blended 40/40/20=9.50]  [fcf_yield=3.9% vs rf=4.6%  spread=-0.7%→modifier=-0.25]</t>
+          <t>Current 25.6x  |  5yr avg 31.2x  |  DCF-implied 14.2x [ref only — not used as benchmark]  [-18% vs benchmark]  [trail=9.69 | fwd_pfcf=25.4x→9.79 | abs=7.5 → blended 40/40/20=9.29]  [fcf_yield=3.9% vs rf=4.6%  spread=-0.7%→modifier=-0.25]</t>
         </is>
       </c>
       <c r="E23" s="131" t="inlineStr">
@@ -10640,7 +10642,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>9.25</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10648,7 +10650,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 25.6x  |  5yr avg 32.6x  |  DCF-implied 14.2x [ref only — not used as benchmark]  [-21% vs benchmark]  [trail=10.00 | fwd_pfcf=25.4x→10.00 | abs=7.5 → blended 40/40/20=9.50]  [fcf_yield=3.9% vs rf=4.6%  spread=-0.7%→modifier=-0.25]</t>
+          <t>Current 25.6x  |  5yr avg 31.2x  |  DCF-implied 14.2x [ref only — not used as benchmark]  [-18% vs benchmark]  [trail=9.69 | fwd_pfcf=25.4x→9.79 | abs=7.5 → blended 40/40/20=9.29]  [fcf_yield=3.9% vs rf=4.6%  spread=-0.7%→modifier=-0.25]</t>
         </is>
       </c>
     </row>
